--- a/result.xlsx
+++ b/result.xlsx
@@ -469,11 +469,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Печатная форма GTUFA04C_КС2_2_24-1156-21_0325_К_ГРС Белорецк_Расчистка.pdf</t>
+          <t>Печатная форма GTUFA02_КС-2(1)_2-ИТЦВ_24-0818-23_0325_1-ИТЦВ_D.pdf</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>574024.48</v>
+        <v>491895.44</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -493,11 +493,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Печатная форма GTUFA04C_КС2_3_24-1156-21_0325_К_ГРС Белорецк_СМР.pdf</t>
+          <t>Печатная форма GTUFA02_КС-2_1-ИТЦВ_24-0818-23_0325_1-ИТЦВ_D.pdf</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10059984.85</v>
+        <v>491895.44</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OA СМР</t>
+          <t>КС2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Печатная форма ОА_11-04-20.pdf</t>
+          <t>Печатная форма GTUFA05_КС-2_3-ИТЦВ_24-0818-23_0325_1-ИТЦВ_D.pdf</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10634009.33</v>
+        <v>14657.41</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -536,64 +536,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OA АВ</t>
+          <t>КС2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Печатная форма ОА_11-04-20.pdf</t>
+          <t>Печатная форма GTUFA05_КС-2_6-ИТЦВ_24-0818-23_0325_1-ИТЦВ_D.pdf</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>319020.28</v>
+        <v>723467.14</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>СФ СМР</t>
+          <t>OA СМР</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Печатная форма Счет-фактура №ГИ250325-0258-24 от 25.03.25.pdf</t>
+          <t>№ОА_12-05-20.pdf от 28.03.25.pdf</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>10634009.33</v>
+        <v>1721915.43</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>СФ АВ</t>
+          <t>OA АВ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Печатная форма Счет-фактура №ГИ250327-0189-24 от 27.03.25.pdf</t>
+          <t>№ОА_12-05-20.pdf от 28.03.25.pdf</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>319020.28</v>
+        <v>51657.46</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>СФ СМР</t>
+          <t>СФ АВ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Печатная форма Счет-фактура №25030023 от 25.03.25.pdf</t>
+          <t>№ГИ250327-0079-24 от 28.03.25.pdf</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>10634009.33</v>
+        <v>51657.46</v>
       </c>
       <c r="D8" s="2" t="n"/>
     </row>
@@ -605,29 +605,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Печатная форма Счет-фактура №ГИ250325-0258-24 от 25.03.25.pdf</t>
+          <t>№ГИ250327-0081-24 от 28.03.25.pdf</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>10634009.33</v>
+        <v>1721915.43</v>
       </c>
       <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>СФ АВ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Печатная форма Счет-фактура №ГИ250327-0189-24 от 27.03.25.pdf</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>319020.28</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="3" t="n"/>
